--- a/reports/be6eb534-f559-4c86-898e-ab2dfef030d7/2025/07/report____________________________________________07_2025.xlsx
+++ b/reports/be6eb534-f559-4c86-898e-ab2dfef030d7/2025/07/report____________________________________________07_2025.xlsx
@@ -82,7 +82,7 @@
     <t>Напомена:</t>
   </si>
   <si>
-    <t>Наплаћен износ у postpaid саобраћају у периоду</t>
+    <t>Наплаћен износ у prepaid саобраћају у периоду</t>
   </si>
   <si>
     <t>1.07.2025 do 31.07.2025</t>
